--- a/survey_templates/046_third_party_risk_assessment_survey--survey_templates.xlsx
+++ b/survey_templates/046_third_party_risk_assessment_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,11 +437,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
     <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -525,10 +525,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>First Page</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Survey Overview</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please answer the questions below to assess the risk of your third-party vendors.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>no</t>
@@ -548,13 +552,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Risk Assessment Ratings</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Vendor Risk Assessment Ratings</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Rate the risk level for the following questions.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -571,10 +579,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Vendors Answers</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Vendor Information</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Please provide the vendor's answers to the following questions.</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>no</t>
@@ -589,17 +601,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>risk_assessment_questions</t>
+          <t>risk_factors</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Risk Assessment Questions</t>
+          <t>Risk Factors</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Please answer the following questions about the third-party vendor.</t>
+          <t>Please answer the following questions about the risk factors.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -621,13 +633,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Has the vendor been vetted and cleared by your company’s security team?</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Has the vendor been vetted and cleared by your company's security team?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Select 'Yes' or 'No'.</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -644,13 +660,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Has the vendor been vetted and cleared by your company’s security team?</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Is the vendor's IT infrastructure in accordance with our security and compliance policies?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Select 'Yes' or 'No'.</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -667,13 +687,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Has the vendor been vetted and cleared by your company’s security team?</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Does the vendor meet our IT security requirements?</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Select 'Yes' or 'No'.</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -690,13 +714,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Is the vendor’s IT infrastructure in accordance with our security and compliance policies?</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Does the vendor meet our IT compliance requirements?</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Select 'Yes' or 'No'.</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -708,18 +736,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>question_5</t>
+          <t>vendor_management_structure</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Does the vendor meet our IT security requirements?</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>What is the vendor's management structure?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Select from the options below.</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -731,18 +763,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>question_6</t>
+          <t>question_5</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Does the vendor meet our IT security requirements?</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>What is the risk level for the vendor's IT infrastructure?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Select from the options below.</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -754,18 +790,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>question_7</t>
+          <t>question_6</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Does the vendor meet our IT security requirements?</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>What is the risk level for the vendor's data handling?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Select from the options below.</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -777,58 +817,66 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compliance_question</t>
+          <t>question_7</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Does the vendor meet our compliance requirements?</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>What is the risk level for the vendor's security practices?</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Select from the options below.</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>regulatory_requirements</t>
+          <t>vendor_info</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Does the vendor meet our regulatory requirements?</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>Vendor Info</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Please provide additional information about the vendor.</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>regulatory_requirements_2</t>
+          <t>notes</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Does the vendor meet our regulatory requirements?</t>
+          <t>Additional Notes</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -846,38 +894,46 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>regulatory_requirements_3</t>
+          <t>vendor_rating</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Does the vendor meet our regulatory requirements?</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>Overall Vendor Rating</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Rate the vendor overall.</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>vendor_management_structure</t>
+          <t>rating_rationale</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>What management structure does the vendor have in place?</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>Rating Rationale</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Please provide a brief explanation for the overall rating.</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>no</t>
@@ -887,205 +943,21 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>vendor_management_structure_2</t>
+          <t>vendor_comments</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>What management structure does the vendor have in place?</t>
+          <t>Vendor Comments</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>vendor_management_structure_3</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>What management structure does the vendor have in place?</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>vendor_management_structure_4</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>What management structure does the vendor have in place?</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>vendor_management_structure_5</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>What management structure does the vendor have in place?</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>vendor_management_structure_6</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>What management structure does the vendor have in place?</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>vendor_management_structure_7</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>What management structure does the vendor have in place?</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>vendor_management_structure_8</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>What management structure does the vendor have in place?</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>vendor_name</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Vendor Name</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1102,12 +974,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C42"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="39" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="37" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1135,12 +1007,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1024,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1169,12 +1041,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1058,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1203,12 +1075,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1220,12 +1092,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1237,12 +1109,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1254,12 +1126,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1143,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1288,12 +1160,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1305,522 +1177,250 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>question_5_choices</t>
+          <t>vendor_management_structure_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>centralized</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>Centralized</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>question_5_choices</t>
+          <t>vendor_management_structure_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>decentralized</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>Decentralized</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>question_6_choices</t>
+          <t>question_5_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>question_6_choices</t>
+          <t>question_5_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>question_7_choices</t>
+          <t>question_5_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>question_7_choices</t>
+          <t>question_6_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>compliance_question_choices</t>
+          <t>question_6_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>compliance_question_choices</t>
+          <t>question_6_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>regulatory_requirements_choices</t>
+          <t>question_7_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>regulatory_requirements_choices</t>
+          <t>question_7_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>regulatory_requirements_2_choices</t>
+          <t>question_7_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>regulatory_requirements_2_choices</t>
+          <t>vendor_rating_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>regulatory_requirements_3_choices</t>
+          <t>vendor_rating_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>regulatory_requirements_3_choices</t>
+          <t>vendor_rating_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>vendor_management_structure_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>{'id':_1,_'label':_true}</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>{'id': 1, 'label': True}</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>vendor_management_structure_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'label':_false}</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'label': False}</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>vendor_management_structure_2_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>{'id':_1,_'label':_true}</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>{'id': 1, 'label': True}</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>vendor_management_structure_2_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'label':_false}</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'label': False}</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>vendor_management_structure_3_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>{'id':_1,_'label':_true}</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>{'id': 1, 'label': True}</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>vendor_management_structure_3_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'label':_false}</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'label': False}</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>vendor_management_structure_4_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>{'id':_1,_'label':_true}</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>{'id': 1, 'label': True}</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>vendor_management_structure_4_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'label':_false}</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'label': False}</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>vendor_management_structure_5_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>{'id':_1,_'label':_true}</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>{'id': 1, 'label': True}</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>vendor_management_structure_5_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'label':_false}</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'label': False}</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>vendor_management_structure_6_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>{'id':_1,_'label':_true}</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>{'id': 1, 'label': True}</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>vendor_management_structure_6_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'label':_false}</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'label': False}</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>vendor_management_structure_7_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>{'id':_1,_'label':_true}</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>{'id': 1, 'label': True}</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>vendor_management_structure_7_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'label':_false}</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'label': False}</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>vendor_management_structure_8_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>{'id':_1,_'label':_true}</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>{'id': 1, 'label': True}</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>vendor_management_structure_8_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>{'id':_2,_'label':_false}</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
